--- a/artfynd/A 46071-2024 artfynd.xlsx
+++ b/artfynd/A 46071-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135460478</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135460990</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1041,6 +1056,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135460630</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1160,6 +1180,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135460991</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1279,8 +1304,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135460480</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 46071-2024 artfynd.xlsx
+++ b/artfynd/A 46071-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135460478</v>
       </c>
       <c r="B2" t="n">
-        <v>57280</v>
+        <v>57285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>135460990</v>
       </c>
       <c r="B3" t="n">
-        <v>57921</v>
+        <v>57926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>135460630</v>
       </c>
       <c r="B4" t="n">
-        <v>58410</v>
+        <v>58415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>135460991</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>135460480</v>
       </c>
       <c r="B6" t="n">
-        <v>58698</v>
+        <v>58703</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 46071-2024 artfynd.xlsx
+++ b/artfynd/A 46071-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135460478</v>
       </c>
       <c r="B2" t="n">
-        <v>57285</v>
+        <v>57287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>135460990</v>
       </c>
       <c r="B3" t="n">
-        <v>57926</v>
+        <v>57928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>135460630</v>
       </c>
       <c r="B4" t="n">
-        <v>58415</v>
+        <v>58417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>135460991</v>
       </c>
       <c r="B5" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>135460480</v>
       </c>
       <c r="B6" t="n">
-        <v>58703</v>
+        <v>58705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
